--- a/voting/025_senior_superlatives_form--voting.xlsx
+++ b/voting/025_senior_superlatives_form--voting.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>senior_superlatives_form</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Senior Superlatives Form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your name?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide your full name.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,41 +547,45 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>senior_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is the Senior Superlatives' name?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide the name of a senior you know.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>student_name</t>
+          <t>relationship</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Student Name</t>
+          <t>What is your relationship to the Senior Superlatives?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,12 +597,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>name_1</t>
+          <t>feelings</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>How do you feel about the Senior Superlatives?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +615,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>senior_superlatives</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Senior Superlatives</t>
+          <t>Additional feedback or comments about the Senior Superlatives?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +638,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>name_2</t>
+          <t>preferences</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>What are your preferences for the Senior Superlatives?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +661,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>name_3</t>
+          <t>demographics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>What is your demographic information?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>name_4</t>
+          <t>experiences</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Can you describe your senior experiences?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +707,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>name_5</t>
+          <t>recommendations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Who do you recommend for Senior Superlatives?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,18 +735,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>name_6</t>
+          <t>confirm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Are you ready to submit?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -753,12 +761,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -781,34 +789,170 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>senior_superlatives_choices</t>
+          <t>relationship_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>senior_superlatives_choices</t>
+          <t>relationship_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>mentor</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Mentor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>relationship_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>colleague</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Colleague</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>relationship_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>classmate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Classmate</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>relationship_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>preferences_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>preferences_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>recommendations_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>recommendations_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>recommendations_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
